--- a/resources/terminology.xlsx
+++ b/resources/terminology.xlsx
@@ -370,6 +370,1650 @@
         </ns0:is>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="31">
+      <ns0:c r="A31" t="inlineStr">
+        <ns0:is>
+          <ns0:t>增量备份</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B31" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Incremental Backup</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="32">
+      <ns0:c r="A32" t="inlineStr">
+        <ns0:is>
+          <ns0:t>启动引导固件</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B32" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Boot Firmware</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="33">
+      <ns0:c r="A33" t="inlineStr">
+        <ns0:is>
+          <ns0:t>云硬盘</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B33" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Elastic Volume Service</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="34">
+      <ns0:c r="A34" t="inlineStr">
+        <ns0:is>
+          <ns0:t>云硬盘备份</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B34" t="inlineStr">
+        <ns0:is>
+          <ns0:t>EVS Backups</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="35">
+      <ns0:c r="A35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>裸金属卷</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Bare Metal  Volume</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="36">
+      <ns0:c r="A36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>存储池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Storage Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="37">
+      <ns0:c r="A37" t="inlineStr">
+        <ns0:is>
+          <ns0:t>块存储池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B37" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Elastic Block Storage Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="38">
+      <ns0:c r="A38" t="inlineStr">
+        <ns0:is>
+          <ns0:t>本地存储池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B38" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Local Storage Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="39">
+      <ns0:c r="A39" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NFS备份池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B39" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NFS Backup Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="40">
+      <ns0:c r="A40" t="inlineStr">
+        <ns0:is>
+          <ns0:t>高可用备份池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B40" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HA Backup Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="41">
+      <ns0:c r="A41" t="inlineStr">
+        <ns0:is>
+          <ns0:t>高可用存储池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B41" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HA Storage Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="42">
+      <ns0:c r="A42" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NFS存储池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B42" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NFS Storage Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="43">
+      <ns0:c r="A43" t="inlineStr">
+        <ns0:is>
+          <ns0:t>高速高可用存储池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B43" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Low-Latency HA Storage Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="44">
+      <ns0:c r="A44" t="inlineStr">
+        <ns0:is>
+          <ns0:t>快照</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B44" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Snapshots</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="45">
+      <ns0:c r="A45" t="inlineStr">
+        <ns0:is>
+          <ns0:t>立即备份</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B45" t="inlineStr">
+        <ns0:is>
+          <ns0:t>One-Click Backup</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="46">
+      <ns0:c r="A46" t="inlineStr">
+        <ns0:is>
+          <ns0:t>纳管</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B46" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Onboard</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="47">
+      <ns0:c r="A47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>扩容</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Expansion</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="48">
+      <ns0:c r="A48" t="inlineStr">
+        <ns0:is>
+          <ns0:t>虚拟私有云</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B48" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Virtual Private Cloud</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="49">
+      <ns0:c r="A49" t="inlineStr">
+        <ns0:is>
+          <ns0:t>网络池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B49" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Network</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="50">
+      <ns0:c r="A50" t="inlineStr">
+        <ns0:is>
+          <ns0:t>子网</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B50" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Subnet</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="51">
+      <ns0:c r="A51" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NAT网关</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B51" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NAT Gateways</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="52">
+      <ns0:c r="A52" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NAT64网关</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B52" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NAT64 Gateways</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="53">
+      <ns0:c r="A53" t="inlineStr">
+        <ns0:is>
+          <ns0:t>对等连接</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B53" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Peering Connections</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="54">
+      <ns0:c r="A54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>安全组</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B54" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Security Groups</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="55">
+      <ns0:c r="A55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>防火墙</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B55" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Firewalls</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="56">
+      <ns0:c r="A56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>浮动IP</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B56" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Floating IP</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="57">
+      <ns0:c r="A57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>路由器</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B57" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Routers</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="58">
+      <ns0:c r="A58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>网络QoS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B58" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Network QoS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="59">
+      <ns0:c r="A59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>负载均衡</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Load Balancers</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="60">
+      <ns0:c r="A60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>DNS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>DNS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="61">
+      <ns0:c r="A61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>流量镜像</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Traffic Mirroring</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="62">
+      <ns0:c r="A62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>经典网络</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Classic Network</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="63">
+      <ns0:c r="A63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>VPC网络</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>VPC Network</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="64">
+      <ns0:c r="A64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>交换机</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Switch</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="65">
+      <ns0:c r="A65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>地址组</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IP Group</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="66">
+      <ns0:c r="A66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>防火墙服务</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FIrewall Service</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="67">
+      <ns0:c r="A67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>网关</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Gateway</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="68">
+      <ns0:c r="A68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>精简模式</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Simplified</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="69">
+      <ns0:c r="A69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>互联模式</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>InterConnected</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="70">
+      <ns0:c r="A70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>组播</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>multicast</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="71">
+      <ns0:c r="A71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>最大传输单元</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MTU</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="72">
+      <ns0:c r="A72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>网段</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CIDR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="73">
+      <ns0:c r="A73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>段ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Segment ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="74">
+      <ns0:c r="A74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IP分配策略</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IP allocation strategy</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="75">
+      <ns0:c r="A75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>随机分配</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B75" t="inlineStr">
+        <ns0:is>
+          <ns0:t>random</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="76">
+      <ns0:c r="A76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>顺序分配</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B76" t="inlineStr">
+        <ns0:is>
+          <ns0:t>sequential</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="77">
+      <ns0:c r="A77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>静态路由</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B77" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Static Routing</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="78">
+      <ns0:c r="A78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IP地址池</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B78" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IP Pool</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="79">
+      <ns0:c r="A79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>虚拟网卡</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B79" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Virtual Nic</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="80">
+      <ns0:c r="A80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>预留IP</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B80" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Reserved IP</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="81">
+      <ns0:c r="A81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>裸金属</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B81" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Bare Metal Server</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="82">
+      <ns0:c r="A82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>带外管理</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B82" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Out-of-Band Management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="83">
+      <ns0:c r="A83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>硬件信息收集</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B83" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Hardware Inspection</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="84">
+      <ns0:c r="A84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>预启动执行环境</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B84" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Preboot Execution Environment</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="85">
+      <ns0:c r="A85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>系统部署</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B85" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Provisioning</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="86">
+      <ns0:c r="A86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>基板管理控制器</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B86" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Baseboard Management Controller</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="87">
+      <ns0:c r="A87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>规格</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B87" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Flavor</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="88">
+      <ns0:c r="A88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>健康检查</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B88" t="inlineStr">
+        <ns0:is>
+          <ns0:t>health check</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="89">
+      <ns0:c r="A89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>监控</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B89" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Monitoring</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="90">
+      <ns0:c r="A90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>告警</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B90" t="inlineStr">
+        <ns0:is>
+          <ns0:t>alerts</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="91">
+      <ns0:c r="A91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>使用率</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B91" t="inlineStr">
+        <ns0:is>
+          <ns0:t>usage</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="92">
+      <ns0:c r="A92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>流速</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B92" t="inlineStr">
+        <ns0:is>
+          <ns0:t>throughput</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="93">
+      <ns0:c r="A93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>包流速</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B93" t="inlineStr">
+        <ns0:is>
+          <ns0:t>packet rate</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="94">
+      <ns0:c r="A94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>运行状态</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B94" t="inlineStr">
+        <ns0:is>
+          <ns0:t>status</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="95">
+      <ns0:c r="A95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>已使用/未使用/总</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B95" t="inlineStr">
+        <ns0:is>
+          <ns0:t>used/free/total</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="96">
+      <ns0:c r="A96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>阈值</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B96" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Threshold</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="97">
+      <ns0:c r="A97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>指标</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B97" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Metrics</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="98">
+      <ns0:c r="A98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>确认</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B98" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Ok</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="99">
+      <ns0:c r="A99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>确定</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B99" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Confirm</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="100">
+      <ns0:c r="A100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>完成</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B100" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Complete</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="101">
+      <ns0:c r="A101" t="inlineStr">
+        <ns0:is>
+          <ns0:t>保存</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B101" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Save</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="102">
+      <ns0:c r="A102" t="inlineStr">
+        <ns0:is>
+          <ns0:t>取消</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B102" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Cancle</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="103">
+      <ns0:c r="A103" t="inlineStr">
+        <ns0:is>
+          <ns0:t>重置</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B103" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Reset</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="104">
+      <ns0:c r="A104" t="inlineStr">
+        <ns0:is>
+          <ns0:t>关闭</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B104" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Close</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="105">
+      <ns0:c r="A105" t="inlineStr">
+        <ns0:is>
+          <ns0:t>上一步</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B105" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Back</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="106">
+      <ns0:c r="A106" t="inlineStr">
+        <ns0:is>
+          <ns0:t>下一步</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B106" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Next</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="107">
+      <ns0:c r="A107" t="inlineStr">
+        <ns0:is>
+          <ns0:t>是</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B107" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Yes</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="108">
+      <ns0:c r="A108" t="inlineStr">
+        <ns0:is>
+          <ns0:t>否</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B108" t="inlineStr">
+        <ns0:is>
+          <ns0:t>No</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="109">
+      <ns0:c r="A109" t="inlineStr">
+        <ns0:is>
+          <ns0:t>更多</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B109" t="inlineStr">
+        <ns0:is>
+          <ns0:t>More</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="110">
+      <ns0:c r="A110" t="inlineStr">
+        <ns0:is>
+          <ns0:t>首页</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B110" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Home</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="111">
+      <ns0:c r="A111" t="inlineStr">
+        <ns0:is>
+          <ns0:t>帮助</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B111" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Help</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="112">
+      <ns0:c r="A112" t="inlineStr">
+        <ns0:is>
+          <ns0:t>主题</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B112" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Change Skin</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="113">
+      <ns0:c r="A113" t="inlineStr">
+        <ns0:is>
+          <ns0:t>大屏</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B113" t="inlineStr">
+        <ns0:is>
+          <ns0:t>View</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="114">
+      <ns0:c r="A114" t="inlineStr">
+        <ns0:is>
+          <ns0:t>关于我们</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B114" t="inlineStr">
+        <ns0:is>
+          <ns0:t>About Us</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="115">
+      <ns0:c r="A115" t="inlineStr">
+        <ns0:is>
+          <ns0:t>刷新</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B115" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Refresh</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="116">
+      <ns0:c r="A116" t="inlineStr">
+        <ns0:is>
+          <ns0:t>搜索</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B116" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Search</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="117">
+      <ns0:c r="A117" t="inlineStr">
+        <ns0:is>
+          <ns0:t>查询</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B117" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Query</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="118">
+      <ns0:c r="A118" t="inlineStr">
+        <ns0:is>
+          <ns0:t>查看</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B118" t="inlineStr">
+        <ns0:is>
+          <ns0:t>View</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="119">
+      <ns0:c r="A119" t="inlineStr">
+        <ns0:is>
+          <ns0:t>过滤表</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B119" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Filter</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="120">
+      <ns0:c r="A120" t="inlineStr">
+        <ns0:is>
+          <ns0:t>默认按照XX过滤</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B120" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Default Filtering By</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="121">
+      <ns0:c r="A121" t="inlineStr">
+        <ns0:is>
+          <ns0:t>无筛选条件</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B121" t="inlineStr">
+        <ns0:is>
+          <ns0:t>No filtering Data</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="122">
+      <ns0:c r="A122" t="inlineStr">
+        <ns0:is>
+          <ns0:t>清空</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B122" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Clear</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="123">
+      <ns0:c r="A123" t="inlineStr">
+        <ns0:is>
+          <ns0:t>创建</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B123" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Create</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="124">
+      <ns0:c r="A124" t="inlineStr">
+        <ns0:is>
+          <ns0:t>增加</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B124" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Add</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="125">
+      <ns0:c r="A125" t="inlineStr">
+        <ns0:is>
+          <ns0:t>编辑</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B125" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Edit</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="126">
+      <ns0:c r="A126" t="inlineStr">
+        <ns0:is>
+          <ns0:t>删除</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B126" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Delete</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="127">
+      <ns0:c r="A127" t="inlineStr">
+        <ns0:is>
+          <ns0:t>当前选中XX条</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B127" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Currently Selected</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="128">
+      <ns0:c r="A128" t="inlineStr">
+        <ns0:is>
+          <ns0:t>操作</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B128" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Operate</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="129">
+      <ns0:c r="A129" t="inlineStr">
+        <ns0:is>
+          <ns0:t>更多操作</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B129" t="inlineStr">
+        <ns0:is>
+          <ns0:t>More</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="130">
+      <ns0:c r="A130" t="inlineStr">
+        <ns0:is>
+          <ns0:t>保存成功</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B130" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Save Success</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="131">
+      <ns0:c r="A131" t="inlineStr">
+        <ns0:is>
+          <ns0:t>添加成功</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B131" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Add Success</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="132">
+      <ns0:c r="A132" t="inlineStr">
+        <ns0:is>
+          <ns0:t>删除成功</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B132" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Delete Success</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="133">
+      <ns0:c r="A133" t="inlineStr">
+        <ns0:is>
+          <ns0:t>自定义</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B133" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Custom</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="134">
+      <ns0:c r="A134" t="inlineStr">
+        <ns0:is>
+          <ns0:t>详情</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B134" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Detail</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="135">
+      <ns0:c r="A135" t="inlineStr">
+        <ns0:is>
+          <ns0:t>摘要</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B135" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Abstract</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="136">
+      <ns0:c r="A136" t="inlineStr">
+        <ns0:is>
+          <ns0:t>基本信息</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B136" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Base Information</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="137">
+      <ns0:c r="A137" t="inlineStr">
+        <ns0:is>
+          <ns0:t>概览</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B137" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Overview</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="138">
+      <ns0:c r="A138" t="inlineStr">
+        <ns0:is>
+          <ns0:t>高级</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B138" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Advanced</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="139">
+      <ns0:c r="A139" t="inlineStr">
+        <ns0:is>
+          <ns0:t>高级配置</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B139" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Advanced Configration</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="140">
+      <ns0:c r="A140" t="inlineStr">
+        <ns0:is>
+          <ns0:t>资源组织</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B140" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Resource Organization</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="141">
+      <ns0:c r="A141" t="inlineStr">
+        <ns0:is>
+          <ns0:t>可用区</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B141" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Availability Zone</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="142">
+      <ns0:c r="A142" t="inlineStr">
+        <ns0:is>
+          <ns0:t>内置可用区</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B142" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Built-in Availability Zone</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="143">
+      <ns0:c r="A143" t="inlineStr">
+        <ns0:is>
+          <ns0:t>物理位置</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B143" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Physical Location</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="144">
+      <ns0:c r="A144" t="inlineStr">
+        <ns0:is>
+          <ns0:t>虚拟数据中心</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B144" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Virtual Data Center</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="145">
+      <ns0:c r="A145" t="inlineStr">
+        <ns0:is>
+          <ns0:t>配额模板管理</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B145" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Quota Template Management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="146">
+      <ns0:c r="A146" t="inlineStr">
+        <ns0:is>
+          <ns0:t>配额</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B146" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Quota</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="147">
+      <ns0:c r="A147" t="inlineStr">
+        <ns0:is>
+          <ns0:t>用户管理</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B147" t="inlineStr">
+        <ns0:is>
+          <ns0:t>User Management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="148">
+      <ns0:c r="A148" t="inlineStr">
+        <ns0:is>
+          <ns0:t>角色管理</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B148" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Role Management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="149">
+      <ns0:c r="A149" t="inlineStr">
+        <ns0:is>
+          <ns0:t>用户组管理</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B149" t="inlineStr">
+        <ns0:is>
+          <ns0:t>User Group Management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="150">
+      <ns0:c r="A150" t="inlineStr">
+        <ns0:is>
+          <ns0:t>任务</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B150" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Task</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="151">
+      <ns0:c r="A151" t="inlineStr">
+        <ns0:is>
+          <ns0:t>普通任务</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B151" t="inlineStr">
+        <ns0:is>
+          <ns0:t>General Task</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="152">
+      <ns0:c r="A152" t="inlineStr">
+        <ns0:is>
+          <ns0:t>系统任务</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B152" t="inlineStr">
+        <ns0:is>
+          <ns0:t>System Task</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="153">
+      <ns0:c r="A153" t="inlineStr">
+        <ns0:is>
+          <ns0:t>定时任务</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B153" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Scheduled Task</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="154">
+      <ns0:c r="A154" t="inlineStr">
+        <ns0:is>
+          <ns0:t>业务流程</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B154" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Business Process</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="155">
+      <ns0:c r="A155" t="inlineStr">
+        <ns0:is>
+          <ns0:t>订单管理</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B155" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Order Management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="156">
+      <ns0:c r="A156" t="inlineStr">
+        <ns0:is>
+          <ns0:t>流程管理</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B156" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Process Management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="157">
+      <ns0:c r="A157" t="inlineStr">
+        <ns0:is>
+          <ns0:t>业务统计</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B157" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Business Statistics</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="158">
+      <ns0:c r="A158" t="inlineStr">
+        <ns0:is>
+          <ns0:t>报表</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B158" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Report</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="159">
+      <ns0:c r="A159" t="inlineStr">
+        <ns0:is>
+          <ns0:t>资源报表</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B159" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Resource Report</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="160">
+      <ns0:c r="A160" t="inlineStr">
+        <ns0:is>
+          <ns0:t>费用报表</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B160" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Cost Report</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="161">
+      <ns0:c r="A161" t="inlineStr">
+        <ns0:is>
+          <ns0:t>业务报表</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B161" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Business Report</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="162">
+      <ns0:c r="A162" t="inlineStr">
+        <ns0:is>
+          <ns0:t>日志报表</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B162" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Log Report</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="163">
+      <ns0:c r="A163" t="inlineStr">
+        <ns0:is>
+          <ns0:t>费用与成本</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B163" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Expense and Cost</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="164">
+      <ns0:c r="A164" t="inlineStr">
+        <ns0:is>
+          <ns0:t>组织账单</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B164" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Organization Bill</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="165">
+      <ns0:c r="A165" t="inlineStr">
+        <ns0:is>
+          <ns0:t>明细账单</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B165" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Detailed Bill</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="166">
+      <ns0:c r="A166" t="inlineStr">
+        <ns0:is>
+          <ns0:t>用量明细</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B166" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Usage Details</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="167">
+      <ns0:c r="A167" t="inlineStr">
+        <ns0:is>
+          <ns0:t>价格配置</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B167" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Price Configuration</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
 </ns0:worksheet>
 </file>